--- a/numerical-workflows/v2/framework/经济/模块产销表/09_玩法_大秘境.xlsx
+++ b/numerical-workflows/v2/framework/经济/模块产销表/09_玩法_大秘境.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="玩法产出" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="资源汇总" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="机器明细" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="玩法产出" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源汇总" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机器明细" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'产销阅读'!$A$1:$J$53</definedName>
@@ -716,7 +716,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>产出:13114.0</t>
+          <t>产出:10114.0</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       <c r="O10" s="5" t="inlineStr"/>
       <c r="P10" s="5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q10" s="5" t="inlineStr"/>
@@ -3553,7 +3553,7 @@
       <c r="O11" s="5" t="inlineStr"/>
       <c r="P11" s="5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q11" s="5" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
       <c r="O12" s="5" t="inlineStr"/>
       <c r="P12" s="5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q12" s="5" t="inlineStr"/>
@@ -3651,7 +3651,7 @@
       <c r="O13" s="5" t="inlineStr"/>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr"/>
@@ -3700,7 +3700,7 @@
       <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr"/>
@@ -3749,7 +3749,7 @@
       <c r="O15" s="5" t="inlineStr"/>
       <c r="P15" s="5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr"/>
@@ -3847,7 +3847,7 @@
       <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="5" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr"/>
@@ -3945,7 +3945,7 @@
       <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr"/>
@@ -3994,7 +3994,7 @@
       <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="5" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr"/>
@@ -4043,7 +4043,7 @@
       <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr"/>
@@ -4092,7 +4092,7 @@
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr"/>
@@ -4141,7 +4141,7 @@
       <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Q23" s="5" t="inlineStr"/>
@@ -4190,7 +4190,7 @@
       <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
       <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
       <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr"/>
@@ -4337,7 +4337,7 @@
       <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr"/>
@@ -4386,7 +4386,7 @@
       <c r="O28" s="5" t="inlineStr"/>
       <c r="P28" s="5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
       <c r="O45" s="5" t="inlineStr"/>
       <c r="P45" s="5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
       <c r="O48" s="5" t="inlineStr"/>
       <c r="P48" s="5" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>150</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -6989,7 +6989,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr"/>
@@ -7087,7 +7087,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr"/>
@@ -7185,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr"/>
@@ -7283,7 +7283,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr"/>
@@ -7381,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr"/>
@@ -7479,7 +7479,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr"/>
@@ -7577,7 +7577,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr"/>
@@ -7675,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr"/>
@@ -7773,7 +7773,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
@@ -7871,7 +7871,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="inlineStr"/>
@@ -8067,7 +8067,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr"/>
@@ -8165,7 +8165,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr"/>
@@ -8263,7 +8263,7 @@
         <v>2</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="inlineStr"/>
@@ -8361,7 +8361,7 @@
         <v>2</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="inlineStr"/>
@@ -8459,7 +8459,7 @@
         <v>2</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
@@ -8557,7 +8557,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
         <v>2</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr"/>
@@ -8753,7 +8753,7 @@
         <v>2</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
@@ -9243,7 +9243,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
@@ -9439,7 +9439,7 @@
         <v>3</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
